--- a/output/zone_monthly_4_03/renewable_enterprise_sales_4_03.xlsx
+++ b/output/zone_monthly_4_03/renewable_enterprise_sales_4_03.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,43 +527,43 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1392736.204</v>
+        <v>1410742.031</v>
       </c>
       <c r="E2" t="n">
         <v>2968.044</v>
       </c>
       <c r="F2" t="n">
-        <v>230063.984</v>
+        <v>230157.291</v>
       </c>
       <c r="G2" t="n">
         <v>142.575</v>
       </c>
       <c r="H2" t="n">
-        <v>81922.777</v>
+        <v>82016.084</v>
       </c>
       <c r="I2" t="n">
         <v>147998.632</v>
       </c>
       <c r="J2" t="n">
-        <v>107902.807</v>
+        <v>108006.219</v>
       </c>
       <c r="K2" t="n">
         <v>3523.786</v>
       </c>
       <c r="L2" t="n">
-        <v>69055.22100000001</v>
+        <v>69158.633</v>
       </c>
       <c r="M2" t="n">
         <v>35323.8</v>
       </c>
       <c r="N2" t="n">
-        <v>1051801.369</v>
+        <v>1069610.477</v>
       </c>
       <c r="O2" t="n">
         <v>1288.685</v>
       </c>
       <c r="P2" t="n">
-        <v>101041.586</v>
+        <v>118850.694</v>
       </c>
       <c r="Q2" t="n">
         <v>948300.8</v>
@@ -589,43 +589,43 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1530071.317</v>
+        <v>1549040.647</v>
       </c>
       <c r="E3" t="n">
         <v>2924.127</v>
       </c>
       <c r="F3" t="n">
-        <v>207312.809</v>
+        <v>207066.222</v>
       </c>
       <c r="G3" t="n">
         <v>6078.594</v>
       </c>
       <c r="H3" t="n">
-        <v>78273.307</v>
+        <v>78026.72</v>
       </c>
       <c r="I3" t="n">
         <v>122960.908</v>
       </c>
       <c r="J3" t="n">
-        <v>108328.441</v>
+        <v>108611.108</v>
       </c>
       <c r="K3" t="n">
         <v>10025.179</v>
       </c>
       <c r="L3" t="n">
-        <v>66326.856</v>
+        <v>66609.523</v>
       </c>
       <c r="M3" t="n">
         <v>31976.406</v>
       </c>
       <c r="N3" t="n">
-        <v>1211505.94</v>
+        <v>1230439.19</v>
       </c>
       <c r="O3" t="n">
         <v>805.069</v>
       </c>
       <c r="P3" t="n">
-        <v>143165.745</v>
+        <v>162098.995</v>
       </c>
       <c r="Q3" t="n">
         <v>1066637.604</v>
@@ -651,43 +651,43 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1675949.263</v>
+        <v>1707161.386</v>
       </c>
       <c r="E4" t="n">
         <v>3986.239</v>
       </c>
       <c r="F4" t="n">
-        <v>208270.462</v>
+        <v>208412.643</v>
       </c>
       <c r="G4" t="n">
         <v>1668.945</v>
       </c>
       <c r="H4" t="n">
-        <v>101310.467</v>
+        <v>101452.648</v>
       </c>
       <c r="I4" t="n">
         <v>105291.05</v>
       </c>
       <c r="J4" t="n">
-        <v>108305.937</v>
+        <v>112639.358</v>
       </c>
       <c r="K4" t="n">
-        <v>9892.365</v>
+        <v>9868.48</v>
       </c>
       <c r="L4" t="n">
-        <v>74557.359</v>
+        <v>78914.66499999999</v>
       </c>
       <c r="M4" t="n">
         <v>23856.213</v>
       </c>
       <c r="N4" t="n">
-        <v>1355386.625</v>
+        <v>1382123.146</v>
       </c>
       <c r="O4" t="n">
         <v>903.572</v>
       </c>
       <c r="P4" t="n">
-        <v>193647.438</v>
+        <v>220383.959</v>
       </c>
       <c r="Q4" t="n">
         <v>1159785.306</v>
@@ -713,43 +713,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1017629.821</v>
+        <v>1054066.966</v>
       </c>
       <c r="E5" t="n">
         <v>4113.915</v>
       </c>
       <c r="F5" t="n">
-        <v>146326.288</v>
+        <v>161391.331</v>
       </c>
       <c r="G5" t="n">
         <v>3487.859</v>
       </c>
       <c r="H5" t="n">
-        <v>95127.886</v>
+        <v>110192.929</v>
       </c>
       <c r="I5" t="n">
         <v>47710.543</v>
       </c>
       <c r="J5" t="n">
-        <v>117660.762</v>
+        <v>123654.482</v>
       </c>
       <c r="K5" t="n">
         <v>9113.887000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>97835.799</v>
+        <v>102688.895</v>
       </c>
       <c r="M5" t="n">
-        <v>10711.076</v>
+        <v>11851.7</v>
       </c>
       <c r="N5" t="n">
-        <v>749528.856</v>
+        <v>764907.238</v>
       </c>
       <c r="O5" t="n">
         <v>967.5599999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>197222.765</v>
+        <v>212601.147</v>
       </c>
       <c r="Q5" t="n">
         <v>550311.42</v>
@@ -775,46 +775,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>959015.955</v>
+        <v>1069486.057</v>
       </c>
       <c r="E6" t="n">
         <v>4312.733</v>
       </c>
       <c r="F6" t="n">
-        <v>157056.942</v>
+        <v>157043.303</v>
       </c>
       <c r="G6" t="n">
         <v>3072.158</v>
       </c>
       <c r="H6" t="n">
-        <v>120237.398</v>
+        <v>120223.759</v>
       </c>
       <c r="I6" t="n">
         <v>33747.386</v>
       </c>
       <c r="J6" t="n">
-        <v>139799.001</v>
+        <v>139573.839</v>
       </c>
       <c r="K6" t="n">
-        <v>9580.138999999999</v>
+        <v>9554.745000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>121442.326</v>
+        <v>121242.558</v>
       </c>
       <c r="M6" t="n">
         <v>8776.536</v>
       </c>
       <c r="N6" t="n">
-        <v>657847.279</v>
+        <v>768556.182</v>
       </c>
       <c r="O6" t="n">
         <v>1225.764</v>
       </c>
       <c r="P6" t="n">
-        <v>162247.818</v>
+        <v>250735.921</v>
       </c>
       <c r="Q6" t="n">
-        <v>493312.189</v>
+        <v>515532.989</v>
       </c>
       <c r="R6" t="n">
         <v>1061.508</v>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>850294.403</v>
+        <v>896492.6409999999</v>
       </c>
       <c r="E7" t="n">
         <v>5097.379</v>
@@ -867,16 +867,16 @@
         <v>5972.802</v>
       </c>
       <c r="N7" t="n">
-        <v>554284.625</v>
+        <v>600482.863</v>
       </c>
       <c r="O7" t="n">
         <v>973.0940000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>213542.845</v>
+        <v>237481.883</v>
       </c>
       <c r="Q7" t="n">
-        <v>339086.346</v>
+        <v>361345.546</v>
       </c>
       <c r="R7" t="n">
         <v>682.34</v>
@@ -899,46 +899,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>987276.691</v>
+        <v>1019873.795</v>
       </c>
       <c r="E8" t="n">
         <v>3416.797</v>
       </c>
       <c r="F8" t="n">
-        <v>136304.379</v>
+        <v>136424.997</v>
       </c>
       <c r="G8" t="n">
         <v>911.824</v>
       </c>
       <c r="H8" t="n">
-        <v>89470.67999999999</v>
+        <v>89591.298</v>
       </c>
       <c r="I8" t="n">
         <v>45921.875</v>
       </c>
       <c r="J8" t="n">
-        <v>104809.29</v>
+        <v>103312.39</v>
       </c>
       <c r="K8" t="n">
-        <v>6768.514</v>
+        <v>6789.489</v>
       </c>
       <c r="L8" t="n">
-        <v>88414.785</v>
+        <v>86896.91</v>
       </c>
       <c r="M8" t="n">
         <v>9625.991</v>
       </c>
       <c r="N8" t="n">
-        <v>742746.225</v>
+        <v>776719.611</v>
       </c>
       <c r="O8" t="n">
         <v>731.394</v>
       </c>
       <c r="P8" t="n">
-        <v>196346.608</v>
+        <v>203875.194</v>
       </c>
       <c r="Q8" t="n">
-        <v>544994.682</v>
+        <v>571439.482</v>
       </c>
       <c r="R8" t="n">
         <v>673.5410000000001</v>
@@ -961,46 +961,46 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>823178.202</v>
+        <v>851316.481</v>
       </c>
       <c r="E9" t="n">
         <v>5330.411</v>
       </c>
       <c r="F9" t="n">
-        <v>148561.11</v>
+        <v>148561.12</v>
       </c>
       <c r="G9" t="n">
         <v>2264.886</v>
       </c>
       <c r="H9" t="n">
-        <v>117958.614</v>
+        <v>117958.624</v>
       </c>
       <c r="I9" t="n">
         <v>28337.61</v>
       </c>
       <c r="J9" t="n">
-        <v>128327.543</v>
+        <v>128386.952</v>
       </c>
       <c r="K9" t="n">
         <v>10274.294</v>
       </c>
       <c r="L9" t="n">
-        <v>111273.106</v>
+        <v>111332.515</v>
       </c>
       <c r="M9" t="n">
         <v>6780.143</v>
       </c>
       <c r="N9" t="n">
-        <v>540959.138</v>
+        <v>569037.998</v>
       </c>
       <c r="O9" t="n">
         <v>1248.341</v>
       </c>
       <c r="P9" t="n">
-        <v>234757.029</v>
+        <v>244211.889</v>
       </c>
       <c r="Q9" t="n">
-        <v>303872.262</v>
+        <v>322496.262</v>
       </c>
       <c r="R9" t="n">
         <v>1081.506</v>
@@ -1023,46 +1023,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>581099.303</v>
+        <v>595899.202</v>
       </c>
       <c r="E10" t="n">
         <v>4779.041</v>
       </c>
       <c r="F10" t="n">
-        <v>129017.998</v>
+        <v>129013.872</v>
       </c>
       <c r="G10" t="n">
         <v>3872.847</v>
       </c>
       <c r="H10" t="n">
-        <v>112934.964</v>
+        <v>112930.838</v>
       </c>
       <c r="I10" t="n">
         <v>12210.187</v>
       </c>
       <c r="J10" t="n">
-        <v>118010.522</v>
+        <v>117292.508</v>
       </c>
       <c r="K10" t="n">
         <v>7428.828</v>
       </c>
       <c r="L10" t="n">
-        <v>108058.233</v>
+        <v>107340.219</v>
       </c>
       <c r="M10" t="n">
         <v>2523.461</v>
       </c>
       <c r="N10" t="n">
-        <v>329291.742</v>
+        <v>344813.781</v>
       </c>
       <c r="O10" t="n">
         <v>1031.324</v>
       </c>
       <c r="P10" t="n">
-        <v>208392.325</v>
+        <v>217335.164</v>
       </c>
       <c r="Q10" t="n">
-        <v>118720.193</v>
+        <v>125299.393</v>
       </c>
       <c r="R10" t="n">
         <v>1147.9</v>
@@ -1085,46 +1085,46 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1265949.006</v>
+        <v>1316636.26</v>
       </c>
       <c r="E11" t="n">
         <v>4416.776</v>
       </c>
       <c r="F11" t="n">
-        <v>204222.211</v>
+        <v>204531.946</v>
       </c>
       <c r="G11" t="n">
         <v>2751.868</v>
       </c>
       <c r="H11" t="n">
-        <v>108365.13</v>
+        <v>108674.865</v>
       </c>
       <c r="I11" t="n">
         <v>93105.213</v>
       </c>
       <c r="J11" t="n">
-        <v>140272.959</v>
+        <v>139939.074</v>
       </c>
       <c r="K11" t="n">
         <v>8068.224</v>
       </c>
       <c r="L11" t="n">
-        <v>108252.719</v>
+        <v>107918.834</v>
       </c>
       <c r="M11" t="n">
         <v>23952.016</v>
       </c>
       <c r="N11" t="n">
-        <v>917037.0600000001</v>
+        <v>967748.464</v>
       </c>
       <c r="O11" t="n">
         <v>944.513</v>
       </c>
       <c r="P11" t="n">
-        <v>185583.683</v>
+        <v>194439.087</v>
       </c>
       <c r="Q11" t="n">
-        <v>729504.152</v>
+        <v>771360.152</v>
       </c>
       <c r="R11" t="n">
         <v>1004.712</v>
@@ -1147,46 +1147,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1939760.095</v>
+        <v>2006990.172</v>
       </c>
       <c r="E12" t="n">
         <v>3349.937</v>
       </c>
       <c r="F12" t="n">
-        <v>253615.312</v>
+        <v>253629.347</v>
       </c>
       <c r="G12" t="n">
         <v>4105.906</v>
       </c>
       <c r="H12" t="n">
-        <v>87253.383</v>
+        <v>87267.41800000001</v>
       </c>
       <c r="I12" t="n">
         <v>162256.023</v>
       </c>
       <c r="J12" t="n">
-        <v>129893.562</v>
+        <v>129897.557</v>
       </c>
       <c r="K12" t="n">
         <v>5355.283</v>
       </c>
       <c r="L12" t="n">
-        <v>84802.836</v>
+        <v>84806.83100000001</v>
       </c>
       <c r="M12" t="n">
         <v>39735.443</v>
       </c>
       <c r="N12" t="n">
-        <v>1552901.284</v>
+        <v>1620113.331</v>
       </c>
       <c r="O12" t="n">
         <v>583.304</v>
       </c>
       <c r="P12" t="n">
-        <v>166583.236</v>
+        <v>173123.283</v>
       </c>
       <c r="Q12" t="n">
-        <v>1384640.439</v>
+        <v>1445312.439</v>
       </c>
       <c r="R12" t="n">
         <v>1094.305</v>
@@ -1209,37 +1209,37 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2016034.271</v>
+        <v>2088732.416</v>
       </c>
       <c r="E13" t="n">
         <v>3406.858</v>
       </c>
       <c r="F13" t="n">
-        <v>216896.777</v>
+        <v>231285.252</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>70919.68399999999</v>
+        <v>85308.159</v>
       </c>
       <c r="I13" t="n">
         <v>145977.093</v>
       </c>
       <c r="J13" t="n">
-        <v>130603.247</v>
+        <v>131120.917</v>
       </c>
       <c r="K13" t="n">
-        <v>638.915</v>
+        <v>643.679</v>
       </c>
       <c r="L13" t="n">
-        <v>93592.39999999999</v>
+        <v>94105.306</v>
       </c>
       <c r="M13" t="n">
         <v>36371.932</v>
       </c>
       <c r="N13" t="n">
-        <v>1665127.389</v>
+        <v>1722919.389</v>
       </c>
       <c r="O13" t="n">
         <v>893.16</v>
@@ -1248,7 +1248,7 @@
         <v>167485.316</v>
       </c>
       <c r="Q13" t="n">
-        <v>1495127.454</v>
+        <v>1552919.454</v>
       </c>
       <c r="R13" t="n">
         <v>1621.459</v>
@@ -1271,37 +1271,37 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1915729.45</v>
+        <v>1988313.518</v>
       </c>
       <c r="E14" t="n">
-        <v>3098.24</v>
+        <v>3571.021</v>
       </c>
       <c r="F14" t="n">
-        <v>249004.167</v>
+        <v>259040.851</v>
       </c>
       <c r="G14" t="n">
         <v>3836.853</v>
       </c>
       <c r="H14" t="n">
-        <v>85249.311</v>
+        <v>91808.898</v>
       </c>
       <c r="I14" t="n">
-        <v>159918.003</v>
+        <v>163395.1</v>
       </c>
       <c r="J14" t="n">
-        <v>138292.183</v>
+        <v>144520.386</v>
       </c>
       <c r="K14" t="n">
-        <v>2442.02</v>
+        <v>2427.69</v>
       </c>
       <c r="L14" t="n">
-        <v>95279.943</v>
+        <v>101522.476</v>
       </c>
       <c r="M14" t="n">
         <v>40570.22</v>
       </c>
       <c r="N14" t="n">
-        <v>1525334.86</v>
+        <v>1581181.26</v>
       </c>
       <c r="O14" t="n">
         <v>1297.06</v>
@@ -1310,7 +1310,7 @@
         <v>106123.547</v>
       </c>
       <c r="Q14" t="n">
-        <v>1416224</v>
+        <v>1472070.4</v>
       </c>
       <c r="R14" t="n">
         <v>1690.253</v>
@@ -1333,37 +1333,37 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1351259.744</v>
+        <v>1421767.991</v>
       </c>
       <c r="E15" t="n">
         <v>3817.473</v>
       </c>
       <c r="F15" t="n">
-        <v>211087.471</v>
+        <v>235142.305</v>
       </c>
       <c r="G15" t="n">
         <v>3603.375</v>
       </c>
       <c r="H15" t="n">
-        <v>108853.218</v>
+        <v>132908.052</v>
       </c>
       <c r="I15" t="n">
         <v>98630.878</v>
       </c>
       <c r="J15" t="n">
-        <v>122408.052</v>
+        <v>134583.065</v>
       </c>
       <c r="K15" t="n">
-        <v>4706.632</v>
+        <v>4679.288</v>
       </c>
       <c r="L15" t="n">
-        <v>94236.298</v>
+        <v>106438.655</v>
       </c>
       <c r="M15" t="n">
         <v>23465.122</v>
       </c>
       <c r="N15" t="n">
-        <v>1013946.748</v>
+        <v>1048225.148</v>
       </c>
       <c r="O15" t="n">
         <v>1124.007</v>
@@ -1372,7 +1372,7 @@
         <v>134607.723</v>
       </c>
       <c r="Q15" t="n">
-        <v>877026.322</v>
+        <v>911304.722</v>
       </c>
       <c r="R15" t="n">
         <v>1188.696</v>
@@ -1395,37 +1395,37 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1617618.222</v>
+        <v>1676921.279</v>
       </c>
       <c r="E16" t="n">
-        <v>5447.694</v>
+        <v>6568.924</v>
       </c>
       <c r="F16" t="n">
-        <v>263083.287</v>
+        <v>270617.553</v>
       </c>
       <c r="G16" t="n">
         <v>3273.572</v>
       </c>
       <c r="H16" t="n">
-        <v>153999.217</v>
+        <v>161533.483</v>
       </c>
       <c r="I16" t="n">
         <v>105810.498</v>
       </c>
       <c r="J16" t="n">
-        <v>157165.661</v>
+        <v>165714.022</v>
       </c>
       <c r="K16" t="n">
         <v>6284.221</v>
       </c>
       <c r="L16" t="n">
-        <v>125216.458</v>
+        <v>133764.819</v>
       </c>
       <c r="M16" t="n">
         <v>25664.982</v>
       </c>
       <c r="N16" t="n">
-        <v>1191921.58</v>
+        <v>1234020.78</v>
       </c>
       <c r="O16" t="n">
         <v>1075.771</v>
@@ -1434,10 +1434,72 @@
         <v>164295.187</v>
       </c>
       <c r="Q16" t="n">
-        <v>1025293.132</v>
+        <v>1067392.332</v>
       </c>
       <c r="R16" t="n">
         <v>1257.49</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>直轉供及躉售</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>04月</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1167871.09</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4788.421</v>
+      </c>
+      <c r="F17" t="n">
+        <v>179619.995</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>130647.627</v>
+      </c>
+      <c r="I17" t="n">
+        <v>48972.368</v>
+      </c>
+      <c r="J17" t="n">
+        <v>141999.261</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3289.416</v>
+      </c>
+      <c r="L17" t="n">
+        <v>127362.64</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11347.205</v>
+      </c>
+      <c r="N17" t="n">
+        <v>841463.4129999999</v>
+      </c>
+      <c r="O17" t="n">
+        <v>834.22</v>
+      </c>
+      <c r="P17" t="n">
+        <v>173315.289</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>665961.222</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1352.682</v>
       </c>
     </row>
   </sheetData>
@@ -2493,7 +2555,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4934227.605</v>
+        <v>4936375.403</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -2523,13 +2585,13 @@
         <v>211448.332</v>
       </c>
       <c r="N17" t="n">
-        <v>3819518.627</v>
+        <v>3821666.425</v>
       </c>
       <c r="O17" t="n">
         <v>91309.409</v>
       </c>
       <c r="P17" t="n">
-        <v>2242166.653</v>
+        <v>2244314.451</v>
       </c>
       <c r="Q17" t="n">
         <v>1466316.283</v>
@@ -2555,7 +2617,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9536572.68942</v>
+        <v>9555743.04042</v>
       </c>
       <c r="E18" t="n">
         <v>40229.342</v>
@@ -2585,13 +2647,13 @@
         <v>182924.213</v>
       </c>
       <c r="N18" t="n">
-        <v>7812612.835</v>
+        <v>7831783.186</v>
       </c>
       <c r="O18" t="n">
         <v>14931.361</v>
       </c>
       <c r="P18" t="n">
-        <v>3062793.043</v>
+        <v>3081963.394</v>
       </c>
       <c r="Q18" t="n">
         <v>4721663.183</v>
@@ -2617,7 +2679,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13375207.129</v>
+        <v>13652913.235</v>
       </c>
       <c r="E19" t="n">
         <v>50673.469</v>
@@ -2647,13 +2709,13 @@
         <v>208407.987</v>
       </c>
       <c r="N19" t="n">
-        <v>10599453.516</v>
+        <v>10877159.622</v>
       </c>
       <c r="O19" t="n">
         <v>15179.676</v>
       </c>
       <c r="P19" t="n">
-        <v>3109830.784</v>
+        <v>3387536.89</v>
       </c>
       <c r="Q19" t="n">
         <v>7464690.304</v>
@@ -2679,46 +2741,46 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15038994.531</v>
+        <v>15566438.054</v>
       </c>
       <c r="E20" t="n">
         <v>48102.257</v>
       </c>
       <c r="F20" t="n">
-        <v>2196128.717</v>
+        <v>2225997.769</v>
       </c>
       <c r="G20" t="n">
         <v>31429.62</v>
       </c>
       <c r="H20" t="n">
-        <v>1186370.222</v>
+        <v>1216239.274</v>
       </c>
       <c r="I20" t="n">
         <v>978328.875</v>
       </c>
       <c r="J20" t="n">
-        <v>1466346.025</v>
+        <v>1474866.358</v>
       </c>
       <c r="K20" t="n">
-        <v>89850.916</v>
+        <v>89827.376</v>
       </c>
       <c r="L20" t="n">
-        <v>1140889.29</v>
+        <v>1148292.539</v>
       </c>
       <c r="M20" t="n">
-        <v>235605.819</v>
+        <v>236746.443</v>
       </c>
       <c r="N20" t="n">
-        <v>11328417.532</v>
+        <v>11817471.67</v>
       </c>
       <c r="O20" t="n">
         <v>11595.78</v>
       </c>
       <c r="P20" t="n">
-        <v>2170016.394</v>
+        <v>2402622.532</v>
       </c>
       <c r="Q20" t="n">
-        <v>9134292.846999999</v>
+        <v>9390740.846999999</v>
       </c>
       <c r="R20" t="n">
         <v>12512.511</v>

--- a/output/zone_monthly_4_03/renewable_enterprise_sales_4_03.xlsx
+++ b/output/zone_monthly_4_03/renewable_enterprise_sales_4_03.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1500,6 +1500,68 @@
       </c>
       <c r="R17" t="n">
         <v>1352.682</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>直轉供及躉售</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>05月</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1276392.715</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7158.665</v>
+      </c>
+      <c r="F18" t="n">
+        <v>211856.457</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>151928.473</v>
+      </c>
+      <c r="I18" t="n">
+        <v>59927.984</v>
+      </c>
+      <c r="J18" t="n">
+        <v>168833.224</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5221.472</v>
+      </c>
+      <c r="L18" t="n">
+        <v>149545.869</v>
+      </c>
+      <c r="M18" t="n">
+        <v>14065.883</v>
+      </c>
+      <c r="N18" t="n">
+        <v>888544.3689999999</v>
+      </c>
+      <c r="O18" t="n">
+        <v>350.642</v>
+      </c>
+      <c r="P18" t="n">
+        <v>180188.241</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>706700.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1304.686</v>
       </c>
     </row>
   </sheetData>

--- a/output/zone_monthly_4_03/renewable_enterprise_sales_4_03.xlsx
+++ b/output/zone_monthly_4_03/renewable_enterprise_sales_4_03.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,6 +1562,68 @@
       </c>
       <c r="R18" t="n">
         <v>1304.686</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>直轉供及躉售</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>06月</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1084017.638</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5234.768</v>
+      </c>
+      <c r="F19" t="n">
+        <v>186623.022</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>126022.06</v>
+      </c>
+      <c r="I19" t="n">
+        <v>60600.962</v>
+      </c>
+      <c r="J19" t="n">
+        <v>139316.283</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6090.895</v>
+      </c>
+      <c r="L19" t="n">
+        <v>123597.517</v>
+      </c>
+      <c r="M19" t="n">
+        <v>9627.870999999999</v>
+      </c>
+      <c r="N19" t="n">
+        <v>752843.5649999999</v>
+      </c>
+      <c r="O19" t="n">
+        <v>610.889</v>
+      </c>
+      <c r="P19" t="n">
+        <v>155236.169</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>595712.6189999999</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1283.888</v>
       </c>
     </row>
   </sheetData>
@@ -1575,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1669,1216 +1731,6 @@
           <t>selling_to_public_utility_geothermal_mwh</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>96年</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>159490.992</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>159490.992</v>
-      </c>
-      <c r="O2" t="n">
-        <v>11353.392</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>148137.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>97年</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>345079.943</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>345079.943</v>
-      </c>
-      <c r="O3" t="n">
-        <v>44758.83</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>300321.113</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>98年</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>459156.275</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>459156.275</v>
-      </c>
-      <c r="O4" t="n">
-        <v>60197.53</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>398958.745</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>99年</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>563031.626</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>563031.626</v>
-      </c>
-      <c r="O5" t="n">
-        <v>71843.03</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>491188.596</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100年</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>733444.626</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>733444.626</v>
-      </c>
-      <c r="O6" t="n">
-        <v>63255.92</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>670188.706</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>101年</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>738794.98</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>738794.98</v>
-      </c>
-      <c r="O7" t="n">
-        <v>84248.09</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>654546.89</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>102年</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>956217.769</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>956217.769</v>
-      </c>
-      <c r="O8" t="n">
-        <v>80928.334</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5815.811</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>869473.624</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>103年</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>865838.472</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>865838.472</v>
-      </c>
-      <c r="O9" t="n">
-        <v>66043.77499999999</v>
-      </c>
-      <c r="P9" t="n">
-        <v>19851.495</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>779943.202</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>104年</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>864623.724</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>864623.724</v>
-      </c>
-      <c r="O10" t="n">
-        <v>47785.426</v>
-      </c>
-      <c r="P10" t="n">
-        <v>29824.561</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>787013.737</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>105年</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>905351.219</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>905351.219</v>
-      </c>
-      <c r="O11" t="n">
-        <v>89175.158</v>
-      </c>
-      <c r="P11" t="n">
-        <v>35969.501</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>780206.5600000001</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>106年</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1089717.588</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1089717.588</v>
-      </c>
-      <c r="O12" t="n">
-        <v>68408.568</v>
-      </c>
-      <c r="P12" t="n">
-        <v>69769.41099999999</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>951539.6090000001</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>107年</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1045951.119</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1045951.119</v>
-      </c>
-      <c r="O13" t="n">
-        <v>71722.97199999999</v>
-      </c>
-      <c r="P13" t="n">
-        <v>84333.606</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>889894.541</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>108年</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1075578.781</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1075578.781</v>
-      </c>
-      <c r="O14" t="n">
-        <v>63868.653</v>
-      </c>
-      <c r="P14" t="n">
-        <v>127763.748</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>883946.38</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>109年</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2225003.54184</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>215821.642</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>93447.033</v>
-      </c>
-      <c r="I15" t="n">
-        <v>122374.609</v>
-      </c>
-      <c r="J15" t="n">
-        <v>37619.02684</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>387.71784</v>
-      </c>
-      <c r="M15" t="n">
-        <v>37231.309</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1971562.873</v>
-      </c>
-      <c r="O15" t="n">
-        <v>63472.833</v>
-      </c>
-      <c r="P15" t="n">
-        <v>442132.081</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1465957.959</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>110年</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>2768802.672</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>552692.528</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>139694.088</v>
-      </c>
-      <c r="I16" t="n">
-        <v>412998.44</v>
-      </c>
-      <c r="J16" t="n">
-        <v>119148.003</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6361.07</v>
-      </c>
-      <c r="M16" t="n">
-        <v>112786.933</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2096962.141</v>
-      </c>
-      <c r="O16" t="n">
-        <v>90494.591</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1157556.015</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>839845.125</v>
-      </c>
-      <c r="R16" t="n">
-        <v>9066.41</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>111年</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>4936375.403</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>812215.7</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>137722.545</v>
-      </c>
-      <c r="I17" t="n">
-        <v>674493.155</v>
-      </c>
-      <c r="J17" t="n">
-        <v>302493.278</v>
-      </c>
-      <c r="K17" t="n">
-        <v>34140.491</v>
-      </c>
-      <c r="L17" t="n">
-        <v>56904.455</v>
-      </c>
-      <c r="M17" t="n">
-        <v>211448.332</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3821666.425</v>
-      </c>
-      <c r="O17" t="n">
-        <v>91309.409</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2244314.451</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1466316.283</v>
-      </c>
-      <c r="R17" t="n">
-        <v>19726.282</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>112年</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>9555743.04042</v>
-      </c>
-      <c r="E18" t="n">
-        <v>40229.342</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1121399.91342</v>
-      </c>
-      <c r="G18" t="n">
-        <v>10005.158</v>
-      </c>
-      <c r="H18" t="n">
-        <v>266634.64542</v>
-      </c>
-      <c r="I18" t="n">
-        <v>844760.11</v>
-      </c>
-      <c r="J18" t="n">
-        <v>562330.599</v>
-      </c>
-      <c r="K18" t="n">
-        <v>49781.497</v>
-      </c>
-      <c r="L18" t="n">
-        <v>329624.889</v>
-      </c>
-      <c r="M18" t="n">
-        <v>182924.213</v>
-      </c>
-      <c r="N18" t="n">
-        <v>7831783.186</v>
-      </c>
-      <c r="O18" t="n">
-        <v>14931.361</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3081963.394</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4721663.183</v>
-      </c>
-      <c r="R18" t="n">
-        <v>13225.248</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>113年</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>13652913.235</v>
-      </c>
-      <c r="E19" t="n">
-        <v>50673.469</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1710868.561</v>
-      </c>
-      <c r="G19" t="n">
-        <v>27870.727</v>
-      </c>
-      <c r="H19" t="n">
-        <v>715265.715</v>
-      </c>
-      <c r="I19" t="n">
-        <v>967732.1189999999</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1014211.583</v>
-      </c>
-      <c r="K19" t="n">
-        <v>88214.46799999999</v>
-      </c>
-      <c r="L19" t="n">
-        <v>717589.128</v>
-      </c>
-      <c r="M19" t="n">
-        <v>208407.987</v>
-      </c>
-      <c r="N19" t="n">
-        <v>10877159.622</v>
-      </c>
-      <c r="O19" t="n">
-        <v>15179.676</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3387536.89</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7464690.304</v>
-      </c>
-      <c r="R19" t="n">
-        <v>9752.752</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>114年</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>15566438.054</v>
-      </c>
-      <c r="E20" t="n">
-        <v>48102.257</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2225997.769</v>
-      </c>
-      <c r="G20" t="n">
-        <v>31429.62</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1216239.274</v>
-      </c>
-      <c r="I20" t="n">
-        <v>978328.875</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1474866.358</v>
-      </c>
-      <c r="K20" t="n">
-        <v>89827.376</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1148292.539</v>
-      </c>
-      <c r="M20" t="n">
-        <v>236746.443</v>
-      </c>
-      <c r="N20" t="n">
-        <v>11817471.67</v>
-      </c>
-      <c r="O20" t="n">
-        <v>11595.78</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2402622.532</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>9390740.846999999</v>
-      </c>
-      <c r="R20" t="n">
-        <v>12512.511</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>直轉供及躉售</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>115年</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
